--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIV/LTAIPT_A63F14.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIV/LTAIPT_A63F14.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="7365"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -12,21 +12,19 @@
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
     <sheet name="Hidden_4" sheetId="5" r:id="rId5"/>
-    <sheet name="Hidden_5" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="Hidden_14">Hidden_1!$A$1:$A$4</definedName>
     <definedName name="Hidden_25">Hidden_2!$A$1:$A$2</definedName>
     <definedName name="Hidden_36">Hidden_3!$A$1:$A$3</definedName>
     <definedName name="Hidden_416">Hidden_4!$A$1:$A$5</definedName>
-    <definedName name="Hidden_523">Hidden_5!$A$1:$A$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="96">
   <si>
     <t>48961</t>
   </si>
@@ -124,12 +122,6 @@
     <t>435941</t>
   </si>
   <si>
-    <t>571922</t>
-  </si>
-  <si>
-    <t>571923</t>
-  </si>
-  <si>
     <t>435937</t>
   </si>
   <si>
@@ -139,9 +131,6 @@
     <t>435951</t>
   </si>
   <si>
-    <t>571924</t>
-  </si>
-  <si>
     <t>435945</t>
   </si>
   <si>
@@ -184,7 +173,7 @@
     <t xml:space="preserve">Clave o nivel del puesto </t>
   </si>
   <si>
-    <t>Denominación del puesto (Redactados con perspectiva de género)</t>
+    <t>Denominación del puesto</t>
   </si>
   <si>
     <t>Denominación del cargo o función</t>
@@ -205,19 +194,13 @@
     <t>Número de la convocatoria</t>
   </si>
   <si>
-    <t>Hipervínculo al documento de la convocatoria, invitación y/o aviso (Redactados con perspectiva de género)</t>
+    <t>Hipervínculo al documento</t>
   </si>
   <si>
     <t>Estado del proceso del concurso (catálogo)</t>
   </si>
   <si>
-    <t>Número total de candidato[a]s registrado[a]s</t>
-  </si>
-  <si>
-    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Total de candidatos hombres</t>
-  </si>
-  <si>
-    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Total de candidatas mujeres</t>
+    <t>Número total de candidatos registrados</t>
   </si>
   <si>
     <t>Nombre(s) de la persona aceptada</t>
@@ -229,10 +212,7 @@
     <t>Segundo apellido de la persona aceptada</t>
   </si>
   <si>
-    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
-  </si>
-  <si>
-    <t>Hipervínculo a la versión pública del acta o documento que al(la) ganador(a) (Redactadas con perspectiva de género)</t>
+    <t>Hipervínculo a la versión pública del acta</t>
   </si>
   <si>
     <t>Hipervínculo al sistema electrónico de convocatorias y/o concursos, en su caso</t>
@@ -250,72 +230,63 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2023</t>
+    <t>73B5607C073372270C95BBC7AB818DDE</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>01/01/2022</t>
+  </si>
+  <si>
+    <t>31/03/2022</t>
+  </si>
+  <si>
+    <t>Convocatoria</t>
+  </si>
+  <si>
+    <t>Abierto al público en general</t>
+  </si>
+  <si>
+    <t>Otro</t>
+  </si>
+  <si>
+    <t>Docencia</t>
+  </si>
+  <si>
+    <t>Docente Hora-Semana-Mes y Docente de Jornada</t>
+  </si>
+  <si>
+    <t>Docente frente a grupo</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>14/02/2022</t>
+  </si>
+  <si>
+    <t>no aplica</t>
+  </si>
+  <si>
+    <t>http://public-file-system.usicamm.gob.mx/2022-2023/ad_media_superior/convocatoria/AEMS_COBACH_029.pdf</t>
+  </si>
+  <si>
+    <t>En proceso</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>USICAMM</t>
+  </si>
+  <si>
+    <t>01/04/2022</t>
   </si>
   <si>
     <t>Concurso</t>
   </si>
   <si>
-    <t>Abierto al público en general</t>
-  </si>
-  <si>
-    <t>Otro</t>
-  </si>
-  <si>
-    <t>Docencia</t>
-  </si>
-  <si>
-    <t>Docente Hora-Semana-Mes y Docente de Jornada</t>
-  </si>
-  <si>
-    <t>Docente frente a grupo</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>20/02/2023</t>
-  </si>
-  <si>
-    <t>No aplica</t>
-  </si>
-  <si>
-    <t>http://public-file-system.usicamm.gob.mx/2023-2024/AD/EMS/convocatoria/AEMS_COBACH_029.pdf</t>
-  </si>
-  <si>
-    <t>En proceso</t>
-  </si>
-  <si>
-    <t>USICAMM</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
-  </si>
-  <si>
-    <t>69EC679024E3ECBE22D026F1FA254B7A</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
-  </si>
-  <si>
-    <t>Convocatoria</t>
-  </si>
-  <si>
-    <t>Docente</t>
-  </si>
-  <si>
-    <t>347</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>199</t>
-  </si>
-  <si>
-    <t>01/07/2023</t>
-  </si>
-  <si>
     <t>Invitación</t>
   </si>
   <si>
@@ -341,12 +312,6 @@
   </si>
   <si>
     <t>Desierto</t>
-  </si>
-  <si>
-    <t>Hombre</t>
-  </si>
-  <si>
-    <t>Mujer</t>
   </si>
 </sst>
 </file>
@@ -739,10 +704,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -750,35 +715,33 @@
     <col min="6" max="6" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="42.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="58.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="90.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="93.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="37" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="38.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="181.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="30" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="33.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="181.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="99.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="84.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="67" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -795,7 +758,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -810,7 +773,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -863,43 +826,34 @@
         <v>12</v>
       </c>
       <c r="S4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="U4" t="s">
         <v>6</v>
       </c>
       <c r="V4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="W4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="X4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA4" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>15</v>
       </c>
@@ -978,19 +932,10 @@
       <c r="AA5" t="s">
         <v>40</v>
       </c>
-      <c r="AB5" t="s">
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1018,194 +963,173 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
-      <c r="AB6" s="4"/>
-      <c r="AC6" s="4"/>
-      <c r="AD6" s="4"/>
-    </row>
-    <row r="7" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="N7" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="P7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="R7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="S7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="T7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="U7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="V7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="T7" s="1" t="s">
+      <c r="W7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="U7" s="1" t="s">
+      <c r="X7" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="V7" s="1" t="s">
+      <c r="Y7" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="W7" s="1" t="s">
+      <c r="Z7" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="X7" s="1" t="s">
+      <c r="AA7" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="Y7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:27" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="Z7" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AA7" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AB7" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AC7" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AD7" s="1" t="s">
+      <c r="F8" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="H8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I8" s="2" t="s">
+      <c r="K8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="P8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="S8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="P8" s="2" t="s">
+      <c r="T8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="X8" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="Y8" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="R8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="Z8" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AC8" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD8" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AD6"/>
+    <mergeCell ref="A6:AA6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1213,21 +1137,18 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E200">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E201">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F201">
       <formula1>Hidden_25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G201">
       <formula1>Hidden_36</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q8:Q200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q8:Q201">
       <formula1>Hidden_416</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X200">
-      <formula1>Hidden_523</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1241,22 +1162,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1271,12 +1192,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1291,17 +1212,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1316,47 +1237,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIV/LTAIPT_A63F14.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIV/LTAIPT_A63F14.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3A5561-7D57-49B1-847E-DB3023D85E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="7365"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -12,19 +18,21 @@
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
     <sheet name="Hidden_4" sheetId="5" r:id="rId5"/>
+    <sheet name="Hidden_5" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="Hidden_14">Hidden_1!$A$1:$A$4</definedName>
     <definedName name="Hidden_25">Hidden_2!$A$1:$A$2</definedName>
     <definedName name="Hidden_36">Hidden_3!$A$1:$A$3</definedName>
     <definedName name="Hidden_416">Hidden_4!$A$1:$A$5</definedName>
+    <definedName name="Hidden_523">Hidden_5!$A$1:$A$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="105">
   <si>
     <t>48961</t>
   </si>
@@ -83,7 +91,7 @@
     <t>435948</t>
   </si>
   <si>
-    <t>435958</t>
+    <t>590131</t>
   </si>
   <si>
     <t>435949</t>
@@ -122,6 +130,12 @@
     <t>435941</t>
   </si>
   <si>
+    <t>571922</t>
+  </si>
+  <si>
+    <t>571923</t>
+  </si>
+  <si>
     <t>435937</t>
   </si>
   <si>
@@ -131,6 +145,9 @@
     <t>435951</t>
   </si>
   <si>
+    <t>571924</t>
+  </si>
+  <si>
     <t>435945</t>
   </si>
   <si>
@@ -140,9 +157,6 @@
     <t>435955</t>
   </si>
   <si>
-    <t>435942</t>
-  </si>
-  <si>
     <t>435947</t>
   </si>
   <si>
@@ -173,10 +187,10 @@
     <t xml:space="preserve">Clave o nivel del puesto </t>
   </si>
   <si>
-    <t>Denominación del puesto</t>
-  </si>
-  <si>
-    <t>Denominación del cargo o función</t>
+    <t>Denominación del puesto (Redactados con perspectiva de género)</t>
+  </si>
+  <si>
+    <t>Denominación del cargo</t>
   </si>
   <si>
     <t>Denominación del área o unidad</t>
@@ -194,13 +208,19 @@
     <t>Número de la convocatoria</t>
   </si>
   <si>
-    <t>Hipervínculo al documento</t>
+    <t>Hipervínculo al documento de la convocatoria, invitación y/o aviso (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Estado del proceso del concurso (catálogo)</t>
   </si>
   <si>
-    <t>Número total de candidatos registrados</t>
+    <t>Número total de candidata(o)s registrada(o)s</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Total de candidatos hombres</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Total de candidatas mujeres</t>
   </si>
   <si>
     <t>Nombre(s) de la persona aceptada</t>
@@ -212,76 +232,91 @@
     <t>Segundo apellido de la persona aceptada</t>
   </si>
   <si>
-    <t>Hipervínculo a la versión pública del acta</t>
-  </si>
-  <si>
-    <t>Hipervínculo al sistema electrónico de convocatorias y/o concursos, en su caso</t>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
+    <t>Hipervínculo a la versión pública del acta o documento que asigne a la persona ganadora (Redactadas con perspectiva de género)</t>
+  </si>
+  <si>
+    <t>En su caso, hipervínculo a la versión pública del sistema electrónico de convocatorias y/o concursos</t>
   </si>
   <si>
     <t>Área(s) responsable(s) que genera(n), posee(n), publica(n) y actualizan la información</t>
   </si>
   <si>
-    <t>Fecha de validación</t>
-  </si>
-  <si>
     <t>Fecha de actualización</t>
   </si>
   <si>
     <t>Nota</t>
   </si>
   <si>
-    <t>73B5607C073372270C95BBC7AB818DDE</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/01/2022</t>
-  </si>
-  <si>
-    <t>31/03/2022</t>
+    <t>2024</t>
   </si>
   <si>
     <t>Convocatoria</t>
   </si>
   <si>
+    <t>Abierto sólo a personas servidoras públicas del sujeto obligado</t>
+  </si>
+  <si>
+    <t>Otro</t>
+  </si>
+  <si>
+    <t>Docente</t>
+  </si>
+  <si>
+    <t>Docente Hora-Semana-Mes y Docente de Jornada</t>
+  </si>
+  <si>
+    <t>Docente frente a grupo</t>
+  </si>
+  <si>
+    <t>Docencia</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>19/02/2024</t>
+  </si>
+  <si>
+    <t>No aplica</t>
+  </si>
+  <si>
+    <t>En proceso</t>
+  </si>
+  <si>
+    <t>USICAMM</t>
+  </si>
+  <si>
+    <t>DD99A73A557B6326623D8C6B29104522</t>
+  </si>
+  <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
     <t>Abierto al público en general</t>
   </si>
   <si>
-    <t>Otro</t>
-  </si>
-  <si>
-    <t>Docencia</t>
-  </si>
-  <si>
-    <t>Docente Hora-Semana-Mes y Docente de Jornada</t>
-  </si>
-  <si>
-    <t>Docente frente a grupo</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>14/02/2022</t>
-  </si>
-  <si>
-    <t>no aplica</t>
-  </si>
-  <si>
-    <t>http://public-file-system.usicamm.gob.mx/2022-2023/ad_media_superior/convocatoria/AEMS_COBACH_029.pdf</t>
-  </si>
-  <si>
-    <t>En proceso</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>USICAMM</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
+    <t>http://usicamm.sep.gob.mx/#/convocatorias</t>
+  </si>
+  <si>
+    <t>Finalizado</t>
+  </si>
+  <si>
+    <t>396</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>239</t>
+  </si>
+  <si>
+    <t>01/10/2024</t>
   </si>
   <si>
     <t>Concurso</t>
@@ -293,9 +328,6 @@
     <t>Aviso</t>
   </si>
   <si>
-    <t>Abierto solo a servidores(as) públicos del Sujeto</t>
-  </si>
-  <si>
     <t>Confianza</t>
   </si>
   <si>
@@ -305,19 +337,22 @@
     <t>En evaluación</t>
   </si>
   <si>
-    <t>Finalizado</t>
-  </si>
-  <si>
     <t>Cancelado</t>
   </si>
   <si>
     <t>Desierto</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -413,6 +448,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -428,44 +466,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -493,14 +531,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -528,6 +583,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -539,209 +611,187 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="53.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="42.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="58.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="93.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="90.85546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="37" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="30" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="33.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="35.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="67" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="69.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="68.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="30" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="110.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="84.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -758,7 +808,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -773,7 +823,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -826,34 +876,40 @@
         <v>12</v>
       </c>
       <c r="S4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U4" t="s">
         <v>6</v>
       </c>
       <c r="V4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y4" t="s">
         <v>11</v>
       </c>
-      <c r="W4" t="s">
+      <c r="Z4" t="s">
         <v>11</v>
       </c>
-      <c r="X4" t="s">
+      <c r="AA4" t="s">
         <v>9</v>
       </c>
-      <c r="Y4" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z4" t="s">
+      <c r="AB4" t="s">
         <v>13</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AC4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>15</v>
       </c>
@@ -932,10 +988,16 @@
       <c r="AA5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB5" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -963,173 +1025,187 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
-    </row>
-    <row r="7" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="AB6" s="4"/>
+      <c r="AC6" s="4"/>
+    </row>
+    <row r="7" spans="1:29" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="U8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="V8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="X8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA8" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="Y8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>78</v>
+      <c r="AB8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AA6"/>
+    <mergeCell ref="A6:AC6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1137,18 +1213,21 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E201">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E198" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F198" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>Hidden_25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G198" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>Hidden_36</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q8:Q201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q8:Q198" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>Hidden_416</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X198" xr:uid="{00000000-0002-0000-0000-000004000000}">
+      <formula1>Hidden_523</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1156,28 +1235,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1186,18 +1265,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1206,23 +1285,23 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1231,33 +1310,53 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
